--- a/raboushee_attendance_2026.xlsx
+++ b/raboushee_attendance_2026.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1597,25 +1597,165 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Official Duty — ✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>11h 00m</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Extended Shift — ⚡ Live Extended Station Duty (07:00 AM – 06:00 PM / 11h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Day Off — 🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Day Off — 🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="14">
-        <f>SUM(F5:F33)</f>
+      <c r="F39" s="14">
+        <f>SUM(F5:F37)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Total Active Shifts</t>
         </is>
       </c>
-      <c r="F36" s="15">
-        <f>COUNTIF(F5:F33, "&gt;0")</f>
+      <c r="F40" s="15">
+        <f>COUNTIF(F5:F37, "&gt;0")</f>
         <v/>
       </c>
     </row>
